--- a/digicode.xlsx
+++ b/digicode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\On Line - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43620A1-CBAB-45EE-BB3A-6F45AB39FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD402A5-D807-4042-80A0-37570229B314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="794">
   <si>
     <t>CODIGO</t>
   </si>
@@ -1632,9 +1632,6 @@
     <t>🤖 Sucripcion x 365 dias. Con tu correo electronico. Incluye Nano Banana + 2TB</t>
   </si>
   <si>
-    <t xml:space="preserve">🤖 Sucripcion x 730 dias. Con tu correo electronico. </t>
-  </si>
-  <si>
     <t>Google One AI Premium Compartido</t>
   </si>
   <si>
@@ -2431,6 +2428,9 @@
   </si>
   <si>
     <t>🤖 Sucripcion x 180 dias. Cuentas nuevas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🤖 Sucripcion x 540 dias. Con tu correo electronico. </t>
   </si>
 </sst>
 </file>
@@ -2882,21 +2882,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9152E929-B650-4928-A033-F3B04FA1DA9E}" name="Tabla1" displayName="Tabla1" ref="A1:K153" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
-  <autoFilter ref="A1:K153" xr:uid="{9152E929-B650-4928-A033-F3B04FA1DA9E}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9152E929-B650-4928-A033-F3B04FA1DA9E}" name="Tabla1" displayName="Tabla1" ref="A1:K154" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
+  <autoFilter ref="A1:K154" xr:uid="{9152E929-B650-4928-A033-F3B04FA1DA9E}">
     <filterColumn colId="2">
-      <filters>
+      <filters blank="1">
         <filter val="1"/>
+        <filter val="10"/>
+        <filter val="100"/>
+        <filter val="2"/>
       </filters>
     </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="CHATGPT"/>
+        <filter val="INTELIGENCIA ARTIFICIAL"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K152">
-    <sortCondition ref="G1:G153"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K153">
+    <sortCondition ref="G1:G154"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{5E7AB560-39D5-48BA-BB2F-55D33E0EF285}" name="CODIGO" dataDxfId="18"/>
@@ -3218,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="9" customWidth="1"/>
@@ -3243,13 +3246,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3269,10 +3272,10 @@
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C2" s="7">
         <v>10</v>
@@ -3281,29 +3284,29 @@
         <v>365</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2" s="3">
         <v>82</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -3315,7 +3318,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>48</v>
@@ -3324,14 +3327,14 @@
         <v>55</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>85</v>
@@ -3346,7 +3349,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>48</v>
@@ -3362,7 +3365,7 @@
     </row>
     <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>86</v>
@@ -3377,7 +3380,7 @@
         <v>80</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>48</v>
@@ -3393,7 +3396,7 @@
     </row>
     <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>87</v>
@@ -3408,7 +3411,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>48</v>
@@ -3424,7 +3427,7 @@
     </row>
     <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>18</v>
@@ -3439,7 +3442,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>48</v>
@@ -3455,10 +3458,10 @@
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
@@ -3470,7 +3473,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>48</v>
@@ -3479,17 +3482,17 @@
         <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C9" s="7">
         <v>10</v>
@@ -3498,10 +3501,10 @@
         <v>365</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>100</v>
@@ -3510,17 +3513,17 @@
         <v>19</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C10" s="7">
         <v>10</v>
@@ -3529,10 +3532,10 @@
         <v>365</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>9</v>
@@ -3541,17 +3544,17 @@
         <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C11" s="7">
         <v>10</v>
@@ -3560,10 +3563,10 @@
         <v>365</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>9</v>
@@ -3572,17 +3575,17 @@
         <v>55</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C12" s="7">
         <v>10</v>
@@ -3591,10 +3594,10 @@
         <v>365</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>9</v>
@@ -3603,17 +3606,17 @@
         <v>55</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -3622,10 +3625,10 @@
         <v>365</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>62</v>
@@ -3634,17 +3637,17 @@
         <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C14" s="7">
         <v>10</v>
@@ -3653,10 +3656,10 @@
         <v>365</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>62</v>
@@ -3665,17 +3668,17 @@
         <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C15" s="7">
         <v>10</v>
@@ -3684,29 +3687,29 @@
         <v>365</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H15" s="3">
         <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
@@ -3715,10 +3718,10 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>94</v>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
@@ -3746,13 +3749,13 @@
         <v>30</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H17" s="3">
         <v>19</v>
@@ -3765,7 +3768,7 @@
     </row>
     <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>521</v>
@@ -3777,10 +3780,10 @@
         <v>30</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>94</v>
@@ -3796,7 +3799,7 @@
     </row>
     <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>72</v>
@@ -3808,10 +3811,10 @@
         <v>30</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>94</v>
@@ -3825,9 +3828,9 @@
       <c r="J19" s="2"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -3839,13 +3842,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H20" s="3">
         <v>186</v>
@@ -3858,7 +3861,7 @@
     </row>
     <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -3870,10 +3873,10 @@
         <v>30</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>82</v>
@@ -3889,7 +3892,7 @@
     </row>
     <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>17</v>
@@ -3901,10 +3904,10 @@
         <v>30</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>82</v>
@@ -3920,10 +3923,10 @@
     </row>
     <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -3932,10 +3935,10 @@
         <v>30</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>82</v>
@@ -3951,10 +3954,10 @@
     </row>
     <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C24" s="7">
         <v>1</v>
@@ -3963,10 +3966,10 @@
         <v>30</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>82</v>
@@ -3982,7 +3985,7 @@
     </row>
     <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>66</v>
@@ -3994,10 +3997,10 @@
         <v>365</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>48</v>
@@ -4013,7 +4016,7 @@
     </row>
     <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
@@ -4025,10 +4028,10 @@
         <v>365</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>48</v>
@@ -4044,7 +4047,7 @@
     </row>
     <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -4056,10 +4059,10 @@
         <v>365</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>49</v>
@@ -4075,7 +4078,7 @@
     </row>
     <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -4087,10 +4090,10 @@
         <v>365</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>49</v>
@@ -4106,7 +4109,7 @@
     </row>
     <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -4118,10 +4121,10 @@
         <v>365</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>48</v>
@@ -4137,7 +4140,7 @@
     </row>
     <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>17</v>
@@ -4149,13 +4152,13 @@
         <v>30</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H30" s="3">
         <v>25</v>
@@ -4168,7 +4171,7 @@
     </row>
     <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>17</v>
@@ -4180,10 +4183,10 @@
         <v>30</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>83</v>
@@ -4199,7 +4202,7 @@
     </row>
     <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>21</v>
@@ -4214,7 +4217,7 @@
         <v>33</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>82</v>
@@ -4230,10 +4233,10 @@
     </row>
     <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -4242,10 +4245,10 @@
         <v>365</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>48</v>
@@ -4254,14 +4257,14 @@
         <v>10</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="6"/>
     </row>
     <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>22</v>
@@ -4276,7 +4279,7 @@
         <v>31</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>48</v>
@@ -4292,7 +4295,7 @@
     </row>
     <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>23</v>
@@ -4307,7 +4310,7 @@
         <v>31</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>48</v>
@@ -4323,10 +4326,10 @@
     </row>
     <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C36" s="7">
         <v>10</v>
@@ -4338,7 +4341,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>100</v>
@@ -4352,15 +4355,15 @@
       <c r="J36" s="2"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C37" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="6">
         <v>365</v>
@@ -4369,10 +4372,10 @@
         <v>10</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H37" s="3">
         <v>10</v>
@@ -4383,15 +4386,15 @@
       <c r="J37" s="2"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C38" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="6">
         <v>365</v>
@@ -4400,10 +4403,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H38" s="3">
         <v>10</v>
@@ -4414,15 +4417,15 @@
       <c r="J38" s="2"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C39" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="6">
         <v>30</v>
@@ -4431,10 +4434,10 @@
         <v>10</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H39" s="3">
         <v>19</v>
@@ -4445,9 +4448,9 @@
       <c r="J39" s="2"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>525</v>
@@ -4462,13 +4465,13 @@
         <v>10</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>526</v>
       </c>
       <c r="H40" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>46</v>
@@ -4476,9 +4479,9 @@
       <c r="J40" s="2"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>68</v>
@@ -4493,13 +4496,13 @@
         <v>10</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>527</v>
+        <v>793</v>
       </c>
       <c r="H41" s="3">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>52</v>
@@ -4507,64 +4510,64 @@
       <c r="J41" s="2"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>618</v>
+        <v>642</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C42" s="7">
         <v>1</v>
       </c>
       <c r="D42" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H42" s="3">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>523</v>
+        <v>52</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>694</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>738</v>
+        <v>645</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>617</v>
       </c>
       <c r="C43" s="7">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>30</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="6">
-        <v>365</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>737</v>
-      </c>
       <c r="F43" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="H43" s="3">
-        <v>19</v>
+        <v>136</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>63</v>
+        <v>523</v>
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="6"/>
@@ -4574,7 +4577,7 @@
         <v>693</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>546</v>
+        <v>737</v>
       </c>
       <c r="C44" s="7">
         <v>10</v>
@@ -4583,16 +4586,16 @@
         <v>365</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" s="3">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>63</v>
@@ -4602,10 +4605,10 @@
     </row>
     <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C45" s="7">
         <v>10</v>
@@ -4614,16 +4617,16 @@
         <v>365</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>547</v>
+        <v>83</v>
       </c>
       <c r="H45" s="3">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>63</v>
@@ -4633,196 +4636,196 @@
     </row>
     <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>743</v>
+        <v>545</v>
       </c>
       <c r="C46" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46" s="6">
-        <v>120</v>
+        <v>365</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>741</v>
+        <v>546</v>
       </c>
       <c r="H46" s="3">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>742</v>
+        <v>63</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="6"/>
     </row>
     <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>631</v>
+        <v>742</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
       </c>
       <c r="D47" s="6">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="H47" s="3">
         <v>19</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>584</v>
+        <v>741</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="6"/>
     </row>
     <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>38</v>
+        <v>630</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
       </c>
       <c r="D48" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H48" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="6"/>
     </row>
     <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>539</v>
+        <v>675</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C49" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D49" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>605</v>
+        <v>49</v>
       </c>
       <c r="H49" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="6"/>
     </row>
     <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>750</v>
+        <v>659</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>538</v>
       </c>
       <c r="C50" s="7">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D50" s="6">
         <v>30</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>94</v>
+        <v>604</v>
       </c>
       <c r="H50" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>96</v>
+        <v>544</v>
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="6"/>
     </row>
     <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>594</v>
+        <v>675</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>749</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>593</v>
+        <v>96</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="6"/>
     </row>
     <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C52" s="7">
         <v>1</v>
@@ -4831,16 +4834,16 @@
         <v>365</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>83</v>
       </c>
       <c r="H52" s="3">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>592</v>
@@ -4850,10 +4853,10 @@
     </row>
     <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>755</v>
+        <v>675</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>594</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4862,29 +4865,29 @@
         <v>365</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>740</v>
+        <v>83</v>
       </c>
       <c r="H53" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>532</v>
+        <v>591</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="6"/>
     </row>
     <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
@@ -4893,29 +4896,29 @@
         <v>365</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>739</v>
       </c>
       <c r="H54" s="3">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>68</v>
+        <v>754</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4924,60 +4927,60 @@
         <v>365</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>524</v>
+        <v>738</v>
       </c>
       <c r="H55" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>52</v>
+        <v>531</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="6"/>
     </row>
     <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>751</v>
+        <v>68</v>
       </c>
       <c r="C56" s="7">
         <v>1</v>
       </c>
       <c r="D56" s="6">
-        <v>90</v>
+        <v>365</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="H56" s="3">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>757</v>
+        <v>52</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="6"/>
     </row>
     <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>758</v>
+        <v>675</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>750</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -4986,29 +4989,29 @@
         <v>90</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>741</v>
+        <v>532</v>
       </c>
       <c r="H57" s="3">
         <v>19</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="6"/>
     </row>
     <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>752</v>
+        <v>675</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>757</v>
       </c>
       <c r="C58" s="7">
         <v>1</v>
@@ -5017,81 +5020,81 @@
         <v>90</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>533</v>
+        <v>740</v>
       </c>
       <c r="H58" s="3">
         <v>19</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="6"/>
     </row>
     <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>571</v>
+        <v>751</v>
       </c>
       <c r="C59" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D59" s="6">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>555</v>
+        <v>747</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="H59" s="3">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>570</v>
+        <v>759</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="6"/>
     </row>
     <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>679</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>590</v>
+        <v>681</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>570</v>
       </c>
       <c r="C60" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D60" s="6">
         <v>365</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
       <c r="H60" s="3">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="6"/>
@@ -5100,8 +5103,8 @@
       <c r="A61" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="B61" s="14" t="s">
-        <v>560</v>
+      <c r="B61" s="12" t="s">
+        <v>589</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5110,29 +5113,29 @@
         <v>365</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="H61" s="3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>568</v>
+        <v>590</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="6"/>
     </row>
     <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>733</v>
+        <v>677</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>559</v>
       </c>
       <c r="C62" s="7">
         <v>1</v>
@@ -5141,29 +5144,29 @@
         <v>365</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>732</v>
+        <v>562</v>
       </c>
       <c r="H62" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>734</v>
+        <v>679</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>732</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5172,19 +5175,19 @@
         <v>365</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>557</v>
+        <v>731</v>
       </c>
       <c r="H63" s="3">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="6"/>
@@ -5193,8 +5196,8 @@
       <c r="A64" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>8</v>
+      <c r="B64" s="9" t="s">
+        <v>733</v>
       </c>
       <c r="C64" s="7">
         <v>1</v>
@@ -5203,16 +5206,16 @@
         <v>365</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>556</v>
       </c>
       <c r="H64" s="3">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>564</v>
@@ -5222,85 +5225,85 @@
     </row>
     <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>763</v>
+        <v>673</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>784</v>
+        <v>8</v>
       </c>
       <c r="C65" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="6">
         <v>365</v>
       </c>
       <c r="E65" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>765</v>
-      </c>
       <c r="H65" s="3">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>786</v>
+        <v>563</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="6"/>
     </row>
     <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="7"/>
+      <c r="A66" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C66" s="7">
+        <v>2</v>
+      </c>
+      <c r="D66" s="6">
+        <v>365</v>
+      </c>
       <c r="E66" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="H66" s="3">
+        <v>90</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>785</v>
+      </c>
       <c r="J66" s="2"/>
       <c r="K66" s="6"/>
     </row>
     <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="C67" s="7">
-        <v>1</v>
-      </c>
-      <c r="D67" s="6">
-        <v>30</v>
-      </c>
+      <c r="A67" s="6"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="7"/>
       <c r="E67" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H67" s="3">
-        <v>5</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>600</v>
-      </c>
+        <v>746</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="6"/>
     </row>
     <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>12</v>
+        <v>652</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>598</v>
       </c>
       <c r="C68" s="7">
         <v>1</v>
@@ -5312,26 +5315,26 @@
         <v>29</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H68" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>42</v>
+        <v>599</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="6"/>
     </row>
     <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>702</v>
+        <v>649</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -5343,7 +5346,7 @@
         <v>29</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>82</v>
@@ -5352,17 +5355,17 @@
         <v>10</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="6"/>
     </row>
     <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>652</v>
+        <v>701</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>602</v>
+        <v>104</v>
       </c>
       <c r="C70" s="7">
         <v>1</v>
@@ -5383,17 +5386,17 @@
         <v>10</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>601</v>
+        <v>43</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="6"/>
     </row>
     <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>729</v>
+        <v>651</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>601</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -5405,26 +5408,26 @@
         <v>29</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="H71" s="3">
         <v>10</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>730</v>
+        <v>600</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="6"/>
     </row>
     <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>13</v>
+        <v>652</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>728</v>
       </c>
       <c r="C72" s="7">
         <v>1</v>
@@ -5436,94 +5439,94 @@
         <v>29</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="H72" s="3">
         <v>10</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>57</v>
+        <v>729</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="6"/>
     </row>
     <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>707</v>
+        <v>648</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
       </c>
       <c r="D73" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="H73" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="6"/>
     </row>
     <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C74" s="7">
         <v>1</v>
       </c>
       <c r="D74" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="H74" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="6"/>
     </row>
     <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>651</v>
+        <v>703</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
       </c>
       <c r="D75" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>29</v>
@@ -5532,23 +5535,23 @@
         <v>627</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H75" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="6"/>
     </row>
     <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>703</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>106</v>
+        <v>650</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C76" s="7">
         <v>1</v>
@@ -5560,56 +5563,56 @@
         <v>29</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="H76" s="3">
         <v>19</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="J76" s="2"/>
-      <c r="K76" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>20</v>
+        <v>702</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
       </c>
       <c r="D77" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>536</v>
+        <v>48</v>
       </c>
       <c r="H77" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="J77" s="2"/>
-      <c r="K77" s="6"/>
+      <c r="K77" s="6" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>20</v>
@@ -5624,13 +5627,13 @@
         <v>29</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H78" s="3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>44</v>
@@ -5640,103 +5643,103 @@
     </row>
     <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>625</v>
+        <v>20</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
       </c>
       <c r="D79" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>83</v>
+        <v>532</v>
       </c>
       <c r="H79" s="3">
         <v>37</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>603</v>
+        <v>44</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>763</v>
+        <v>700</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>764</v>
+        <v>624</v>
       </c>
       <c r="C80" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="6">
         <v>365</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>749</v>
+        <v>29</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>765</v>
+        <v>83</v>
       </c>
       <c r="H80" s="3">
-        <v>625</v>
+        <v>37</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>766</v>
+        <v>602</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="6"/>
     </row>
     <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>656</v>
+        <v>762</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>98</v>
+        <v>763</v>
       </c>
       <c r="C81" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" s="6">
         <v>365</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>32</v>
+        <v>748</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>99</v>
+        <v>764</v>
       </c>
       <c r="H81" s="3">
-        <v>10</v>
+        <v>625</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>97</v>
+        <v>765</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="6"/>
     </row>
     <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C82" s="7">
         <v>1</v>
@@ -5748,26 +5751,26 @@
         <v>32</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="H82" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>708</v>
+        <v>653</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>617</v>
+        <v>14</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -5779,26 +5782,26 @@
         <v>32</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>623</v>
+        <v>9</v>
       </c>
       <c r="H83" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>619</v>
+        <v>45</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="6"/>
     </row>
     <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
@@ -5810,32 +5813,32 @@
         <v>32</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>9</v>
+        <v>622</v>
       </c>
       <c r="H84" s="3">
         <v>19</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>596</v>
+        <v>618</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>92</v>
+        <v>596</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
       </c>
       <c r="D85" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>32</v>
@@ -5847,51 +5850,51 @@
         <v>9</v>
       </c>
       <c r="H85" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>91</v>
+        <v>595</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="6"/>
     </row>
     <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>710</v>
+        <v>654</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C86" s="7">
         <v>1</v>
       </c>
       <c r="D86" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>32</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="H86" s="3">
         <v>28</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="6"/>
     </row>
     <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -5903,26 +5906,26 @@
         <v>32</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H87" s="3">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="6"/>
     </row>
     <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C88" s="7">
         <v>1</v>
@@ -5934,57 +5937,57 @@
         <v>32</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H88" s="3">
         <v>37</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="6"/>
     </row>
     <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>537</v>
+        <v>711</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
       </c>
       <c r="D89" s="6">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H89" s="3">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>542</v>
+        <v>71</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="6"/>
     </row>
     <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>108</v>
+        <v>536</v>
       </c>
       <c r="C90" s="7">
         <v>1</v>
@@ -5996,7 +5999,7 @@
         <v>30</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>82</v>
@@ -6005,17 +6008,17 @@
         <v>8</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="6"/>
     </row>
     <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>24</v>
+        <v>661</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -6027,26 +6030,26 @@
         <v>30</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H91" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>35</v>
+        <v>542</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="6"/>
     </row>
     <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>715</v>
+        <v>662</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>613</v>
+        <v>24</v>
       </c>
       <c r="C92" s="7">
         <v>1</v>
@@ -6058,26 +6061,26 @@
         <v>30</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H92" s="3">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>614</v>
+        <v>35</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="6"/>
     </row>
     <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>664</v>
+        <v>714</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>26</v>
+        <v>612</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -6095,17 +6098,17 @@
         <v>82</v>
       </c>
       <c r="H93" s="3">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>40</v>
+        <v>613</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="6"/>
     </row>
     <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>26</v>
@@ -6120,13 +6123,13 @@
         <v>30</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="H94" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>40</v>
@@ -6136,10 +6139,10 @@
     </row>
     <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>551</v>
+        <v>664</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -6151,26 +6154,26 @@
         <v>30</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="H95" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="6"/>
     </row>
     <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>716</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>552</v>
+        <v>665</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>550</v>
       </c>
       <c r="C96" s="7">
         <v>1</v>
@@ -6182,26 +6185,26 @@
         <v>30</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H96" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>41</v>
+        <v>549</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="6"/>
     </row>
     <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -6213,13 +6216,13 @@
         <v>30</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="H97" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>41</v>
@@ -6229,10 +6232,10 @@
     </row>
     <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>611</v>
+        <v>716</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="C98" s="7">
         <v>1</v>
@@ -6244,26 +6247,26 @@
         <v>30</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="H98" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>615</v>
+        <v>41</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="6"/>
     </row>
     <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>657</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>25</v>
+        <v>717</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>610</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -6281,17 +6284,17 @@
         <v>82</v>
       </c>
       <c r="H99" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>534</v>
+        <v>614</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="6"/>
     </row>
     <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>25</v>
@@ -6306,26 +6309,26 @@
         <v>30</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G100" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H100" s="3">
+        <v>10</v>
+      </c>
+      <c r="I100" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="H100" s="3">
-        <v>25</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="6"/>
     </row>
     <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>713</v>
+        <v>666</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="C101" s="7">
         <v>1</v>
@@ -6337,23 +6340,23 @@
         <v>30</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="H101" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="6"/>
     </row>
     <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>109</v>
@@ -6368,26 +6371,26 @@
         <v>30</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="H102" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="6"/>
     </row>
     <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
-        <v>658</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>728</v>
+        <v>713</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C103" s="7">
         <v>1</v>
@@ -6402,23 +6405,23 @@
         <v>627</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="H103" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="6"/>
     </row>
     <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>659</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>535</v>
+        <v>657</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>727</v>
       </c>
       <c r="C104" s="7">
         <v>1</v>
@@ -6430,26 +6433,26 @@
         <v>30</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H104" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>56</v>
+        <v>540</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="6"/>
     </row>
     <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C105" s="7">
         <v>1</v>
@@ -6461,13 +6464,13 @@
         <v>30</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="H105" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>56</v>
@@ -6479,8 +6482,8 @@
       <c r="A106" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="B106" s="9" t="s">
-        <v>538</v>
+      <c r="B106" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="C106" s="7">
         <v>1</v>
@@ -6492,26 +6495,26 @@
         <v>30</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="H106" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>544</v>
+        <v>56</v>
       </c>
       <c r="J106" s="2"/>
       <c r="K106" s="6"/>
     </row>
     <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>719</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>612</v>
+        <v>667</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>537</v>
       </c>
       <c r="C107" s="7">
         <v>1</v>
@@ -6520,29 +6523,29 @@
         <v>30</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>748</v>
+        <v>30</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H107" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>616</v>
+        <v>543</v>
       </c>
       <c r="J107" s="2"/>
       <c r="K107" s="6"/>
     </row>
     <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>670</v>
+        <v>718</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>93</v>
+        <v>611</v>
       </c>
       <c r="C108" s="7">
         <v>1</v>
@@ -6551,26 +6554,26 @@
         <v>30</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>30</v>
+        <v>747</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H108" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>58</v>
+        <v>615</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="6"/>
     </row>
     <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
-        <v>721</v>
+        <v>669</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>93</v>
@@ -6585,13 +6588,13 @@
         <v>30</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>605</v>
+        <v>95</v>
       </c>
       <c r="H109" s="3">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>58</v>
@@ -6604,7 +6607,7 @@
         <v>720</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>622</v>
+        <v>93</v>
       </c>
       <c r="C110" s="7">
         <v>1</v>
@@ -6616,13 +6619,13 @@
         <v>30</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>95</v>
+        <v>604</v>
       </c>
       <c r="H110" s="3">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>58</v>
@@ -6632,10 +6635,10 @@
     </row>
     <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
-        <v>672</v>
+        <v>719</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="C111" s="7">
         <v>1</v>
@@ -6644,19 +6647,19 @@
         <v>30</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>577</v>
+        <v>30</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H111" s="3">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>607</v>
+        <v>58</v>
       </c>
       <c r="J111" s="2"/>
       <c r="K111" s="6"/>
@@ -6666,7 +6669,7 @@
         <v>671</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="C112" s="7">
         <v>1</v>
@@ -6675,29 +6678,29 @@
         <v>30</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H112" s="3">
         <v>10</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="6"/>
     </row>
     <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
-        <v>723</v>
+        <v>670</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>573</v>
+        <v>620</v>
       </c>
       <c r="C113" s="7">
         <v>1</v>
@@ -6706,19 +6709,19 @@
         <v>30</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="H113" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J113" s="2"/>
       <c r="K113" s="6"/>
@@ -6727,7 +6730,7 @@
       <c r="A114" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="2" t="s">
         <v>572</v>
       </c>
       <c r="C114" s="7">
@@ -6737,16 +6740,16 @@
         <v>30</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="H114" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>578</v>
@@ -6756,10 +6759,10 @@
     </row>
     <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>788</v>
+        <v>571</v>
       </c>
       <c r="C115" s="7">
         <v>1</v>
@@ -6768,29 +6771,29 @@
         <v>30</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>627</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H115" s="3">
         <v>19</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>789</v>
+        <v>577</v>
       </c>
       <c r="J115" s="2"/>
       <c r="K115" s="6"/>
     </row>
     <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>574</v>
+        <v>721</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>787</v>
       </c>
       <c r="C116" s="7">
         <v>1</v>
@@ -6799,29 +6802,29 @@
         <v>30</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="H116" s="3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>580</v>
+        <v>788</v>
       </c>
       <c r="J116" s="2"/>
       <c r="K116" s="6"/>
     </row>
     <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
-        <v>725</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>575</v>
+        <v>723</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="C117" s="7">
         <v>1</v>
@@ -6830,67 +6833,88 @@
         <v>30</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="H117" s="3">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J117" s="2"/>
       <c r="K117" s="6"/>
     </row>
     <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>582</v>
+        <v>724</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>574</v>
       </c>
       <c r="C118" s="7">
         <v>1</v>
       </c>
       <c r="D118" s="6">
-        <v>365</v>
+        <v>30</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>83</v>
+        <v>575</v>
       </c>
       <c r="H118" s="3">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="6"/>
     </row>
     <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="6"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="7"/>
-      <c r="F119" s="6"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="2"/>
+      <c r="A119" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C119" s="7">
+        <v>1</v>
+      </c>
+      <c r="D119" s="6">
+        <v>365</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H119" s="3">
+        <v>100</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>582</v>
+      </c>
       <c r="J119" s="2"/>
       <c r="K119" s="6"/>
     </row>
     <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
-      <c r="B120" s="9"/>
+      <c r="B120" s="2"/>
       <c r="C120" s="7"/>
       <c r="F120" s="6"/>
       <c r="H120" s="3"/>
@@ -6900,7 +6924,7 @@
     </row>
     <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
-      <c r="B121" s="2"/>
+      <c r="B121" s="9"/>
       <c r="C121" s="7"/>
       <c r="F121" s="6"/>
       <c r="H121" s="3"/>
@@ -6920,7 +6944,7 @@
     </row>
     <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
-      <c r="B123" s="9"/>
+      <c r="B123" s="2"/>
       <c r="C123" s="7"/>
       <c r="F123" s="6"/>
       <c r="H123" s="3"/>
@@ -6930,7 +6954,7 @@
     </row>
     <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
-      <c r="B124" s="2"/>
+      <c r="B124" s="9"/>
       <c r="C124" s="7"/>
       <c r="F124" s="6"/>
       <c r="H124" s="3"/>
@@ -6960,7 +6984,7 @@
     </row>
     <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
-      <c r="B127" s="9"/>
+      <c r="B127" s="2"/>
       <c r="C127" s="7"/>
       <c r="F127" s="6"/>
       <c r="H127" s="3"/>
@@ -6970,7 +6994,7 @@
     </row>
     <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
-      <c r="B128" s="2"/>
+      <c r="B128" s="9"/>
       <c r="C128" s="7"/>
       <c r="F128" s="6"/>
       <c r="H128" s="3"/>
@@ -6990,7 +7014,7 @@
     </row>
     <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
-      <c r="B130" s="9"/>
+      <c r="B130" s="2"/>
       <c r="C130" s="7"/>
       <c r="F130" s="6"/>
       <c r="H130" s="3"/>
@@ -7000,7 +7024,7 @@
     </row>
     <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
-      <c r="B131" s="2"/>
+      <c r="B131" s="9"/>
       <c r="C131" s="7"/>
       <c r="F131" s="6"/>
       <c r="H131" s="3"/>
@@ -7030,7 +7054,7 @@
     </row>
     <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
-      <c r="B134" s="9"/>
+      <c r="B134" s="2"/>
       <c r="C134" s="7"/>
       <c r="F134" s="6"/>
       <c r="H134" s="3"/>
@@ -7040,7 +7064,7 @@
     </row>
     <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
-      <c r="B135" s="2"/>
+      <c r="B135" s="9"/>
       <c r="C135" s="7"/>
       <c r="F135" s="6"/>
       <c r="H135" s="3"/>
@@ -7059,39 +7083,18 @@
       <c r="K136" s="6"/>
     </row>
     <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C137" s="7">
-        <v>1</v>
-      </c>
-      <c r="D137" s="6">
-        <v>30</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>748</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H137" s="3">
-        <v>10</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>761</v>
-      </c>
+      <c r="A137" s="6"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="7"/>
+      <c r="F137" s="6"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="2"/>
       <c r="J137" s="2"/>
       <c r="K137" s="6"/>
     </row>
     <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>753</v>
@@ -7100,63 +7103,63 @@
         <v>1</v>
       </c>
       <c r="D138" s="6">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>756</v>
+        <v>94</v>
       </c>
       <c r="H138" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="6"/>
     </row>
     <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
-        <v>763</v>
+        <v>675</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="C139" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" s="6">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="H139" s="3">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="J139" s="2"/>
       <c r="K139" s="6"/>
     </row>
     <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C140" s="7">
         <v>2</v>
@@ -7165,26 +7168,26 @@
         <v>365</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H140" s="3">
         <v>150</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="6"/>
     </row>
     <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>768</v>
@@ -7196,16 +7199,16 @@
         <v>365</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="H141" s="3">
-        <v>276</v>
+        <v>150</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>773</v>
@@ -7215,10 +7218,10 @@
     </row>
     <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C142" s="7">
         <v>2</v>
@@ -7227,29 +7230,29 @@
         <v>365</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="H142" s="3">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="6"/>
     </row>
     <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C143" s="7">
         <v>2</v>
@@ -7258,16 +7261,16 @@
         <v>365</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H143" s="3">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>775</v>
@@ -7277,10 +7280,10 @@
     </row>
     <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="B144" s="14" t="s">
-        <v>791</v>
+        <v>762</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>771</v>
       </c>
       <c r="C144" s="7">
         <v>2</v>
@@ -7289,29 +7292,29 @@
         <v>365</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="H144" s="3">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="J144" s="2"/>
       <c r="K144" s="6"/>
     </row>
     <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>779</v>
+        <v>762</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>790</v>
       </c>
       <c r="C145" s="7">
         <v>2</v>
@@ -7320,28 +7323,28 @@
         <v>365</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H145" s="3">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="J145" s="2"/>
       <c r="K145" s="6"/>
     </row>
     <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="B146" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>778</v>
       </c>
       <c r="C146" s="7">
@@ -7351,29 +7354,29 @@
         <v>365</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H146" s="3">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="6"/>
     </row>
     <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C147" s="7">
         <v>2</v>
@@ -7382,60 +7385,60 @@
         <v>365</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="H147" s="3">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="J147" s="2"/>
       <c r="K147" s="6"/>
     </row>
     <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>782</v>
+        <v>762</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>777</v>
       </c>
       <c r="C148" s="7">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D148" s="6">
         <v>365</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="H148" s="3">
-        <v>273</v>
+        <v>100</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="6"/>
     </row>
     <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C149" s="7">
         <v>10</v>
@@ -7444,61 +7447,60 @@
         <v>365</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H149" s="3">
-        <v>392</v>
+        <v>273</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="6"/>
     </row>
     <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>782</v>
+        <v>753</v>
       </c>
       <c r="C150" s="7">
         <v>10</v>
       </c>
       <c r="D150" s="6">
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="H150" s="3">
-        <f>+H148*2</f>
-        <v>546</v>
+        <v>392</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J150" s="2"/>
       <c r="K150" s="6"/>
     </row>
     <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="C151" s="7">
         <v>10</v>
@@ -7507,98 +7509,127 @@
         <v>730</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H151" s="3">
-        <v>555</v>
+        <f>+H149*2</f>
+        <v>546</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J151" s="2"/>
       <c r="K151" s="6"/>
     </row>
     <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>700</v>
+        <v>762</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C152" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D152" s="6">
-        <v>120</v>
+        <v>730</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>80</v>
+        <v>748</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="H152" s="3">
-        <v>19</v>
+        <v>555</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="J152" s="2"/>
       <c r="K152" s="6"/>
     </row>
     <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="B153" s="9" t="s">
-        <v>785</v>
+        <v>699</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>745</v>
       </c>
       <c r="C153" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" s="6">
-        <v>365</v>
+        <v>120</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>749</v>
+        <v>80</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>765</v>
+        <v>789</v>
       </c>
       <c r="H153" s="3">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B154" s="2"/>
-      <c r="I154" s="2"/>
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C154" s="7">
+        <v>2</v>
+      </c>
+      <c r="D154" s="6">
+        <v>365</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="H154" s="3">
+        <v>120</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="J154" s="2"/>
+      <c r="K154" s="6"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B155" s="2"/>
       <c r="I155" s="2"/>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B156" s="9"/>
+      <c r="B156" s="2"/>
       <c r="I156" s="2"/>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B157" s="9"/>
       <c r="I157" s="2"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7610,43 +7641,46 @@
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I160" s="2"/>
     </row>
+    <row r="161" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I161" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C153">
+  <conditionalFormatting sqref="C2:C154">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K91 K94 K100 K128 K139:K141">
+  <conditionalFormatting sqref="K95 K101 K129 K140:K142 K2:K92">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"OFICIAL"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="I46" r:id="rId1" xr:uid="{18D7DB11-1CE3-45D8-B5D3-A13C26008BA2}"/>
+    <hyperlink ref="I47" r:id="rId1" xr:uid="{18D7DB11-1CE3-45D8-B5D3-A13C26008BA2}"/>
     <hyperlink ref="I8" r:id="rId2" xr:uid="{26E6168E-174A-4DEA-B3CF-E63FDAD51E74}"/>
-    <hyperlink ref="I56" r:id="rId3" xr:uid="{42DF7D4B-CF25-47B7-86D8-0948935612C8}"/>
-    <hyperlink ref="I57" r:id="rId4" xr:uid="{D23D1E70-DEA7-4F34-B64B-C2900086741A}"/>
-    <hyperlink ref="I58" r:id="rId5" xr:uid="{A3346D48-87CE-485E-9FB9-77847D25DF05}"/>
-    <hyperlink ref="I137" r:id="rId6" xr:uid="{B6F068AA-5E4E-4ABA-9220-5472ACB28D23}"/>
-    <hyperlink ref="I138" r:id="rId7" xr:uid="{233745DC-A78B-46DB-8C6A-823324062471}"/>
-    <hyperlink ref="I80" r:id="rId8" xr:uid="{7AC13033-F49D-4C72-8B6C-5A0918355296}"/>
-    <hyperlink ref="I139" r:id="rId9" xr:uid="{CE1FF000-E342-4323-A6B5-A96E54FA2823}"/>
-    <hyperlink ref="I141" r:id="rId10" xr:uid="{E7DEEF67-D046-41EB-8C07-EA6EE83253DA}"/>
-    <hyperlink ref="I140" r:id="rId11" xr:uid="{BC4F8482-E53B-46A0-B2F2-9D832E60BEC5}"/>
-    <hyperlink ref="I143" r:id="rId12" xr:uid="{F8B79711-7EAF-402B-8571-0459BDDDDC95}"/>
-    <hyperlink ref="I142" r:id="rId13" xr:uid="{C3F7B3F2-0A6E-4F0B-BCD7-F5DE7D59DDB3}"/>
-    <hyperlink ref="I144" r:id="rId14" xr:uid="{CA658280-90CD-42F3-BEED-E5DFF7EC13E4}"/>
-    <hyperlink ref="I146" r:id="rId15" xr:uid="{67CCFD3A-D3CB-4A94-B0E5-3634235BC3EA}"/>
-    <hyperlink ref="I147" r:id="rId16" xr:uid="{8E62DC48-8448-426E-BF8D-9DA1101F02D8}"/>
-    <hyperlink ref="I148" r:id="rId17" xr:uid="{99981094-7FC6-4754-9372-6CA07364CF17}"/>
-    <hyperlink ref="I149:I151" r:id="rId18" display="https://production-tailoy-repo-magento-statics.s3.amazonaws.com/imagenes/872x872/productos/i/a/n/antivirus-kaspersky-premium-10-dispositivos-2-anos-69606-default-1.jpg" xr:uid="{36C26BAA-89AC-4AF3-B0BE-D1F46C3523D3}"/>
-    <hyperlink ref="I65" r:id="rId19" xr:uid="{7E45C6FB-35DE-4723-800B-AC36B407BEBE}"/>
-    <hyperlink ref="I153" r:id="rId20" xr:uid="{234DB036-E655-484A-A5EB-6C9CAA3397EF}"/>
-    <hyperlink ref="I115" r:id="rId21" xr:uid="{B6A80480-5CD4-4C3E-80BF-0AC484902FC9}"/>
-    <hyperlink ref="I145" r:id="rId22" xr:uid="{FDE00E9F-E9D7-4F6D-84CF-E74FF647C404}"/>
-    <hyperlink ref="I107" r:id="rId23" xr:uid="{FE47A1B0-EBAA-42E2-A121-ABE74DE0175F}"/>
-    <hyperlink ref="I152" r:id="rId24" xr:uid="{7DAF1DB8-167E-4413-8B5E-16E91C8238CE}"/>
+    <hyperlink ref="I57" r:id="rId3" xr:uid="{42DF7D4B-CF25-47B7-86D8-0948935612C8}"/>
+    <hyperlink ref="I58" r:id="rId4" xr:uid="{D23D1E70-DEA7-4F34-B64B-C2900086741A}"/>
+    <hyperlink ref="I59" r:id="rId5" xr:uid="{A3346D48-87CE-485E-9FB9-77847D25DF05}"/>
+    <hyperlink ref="I138" r:id="rId6" xr:uid="{B6F068AA-5E4E-4ABA-9220-5472ACB28D23}"/>
+    <hyperlink ref="I139" r:id="rId7" xr:uid="{233745DC-A78B-46DB-8C6A-823324062471}"/>
+    <hyperlink ref="I81" r:id="rId8" xr:uid="{7AC13033-F49D-4C72-8B6C-5A0918355296}"/>
+    <hyperlink ref="I140" r:id="rId9" xr:uid="{CE1FF000-E342-4323-A6B5-A96E54FA2823}"/>
+    <hyperlink ref="I142" r:id="rId10" xr:uid="{E7DEEF67-D046-41EB-8C07-EA6EE83253DA}"/>
+    <hyperlink ref="I141" r:id="rId11" xr:uid="{BC4F8482-E53B-46A0-B2F2-9D832E60BEC5}"/>
+    <hyperlink ref="I144" r:id="rId12" xr:uid="{F8B79711-7EAF-402B-8571-0459BDDDDC95}"/>
+    <hyperlink ref="I143" r:id="rId13" xr:uid="{C3F7B3F2-0A6E-4F0B-BCD7-F5DE7D59DDB3}"/>
+    <hyperlink ref="I145" r:id="rId14" xr:uid="{CA658280-90CD-42F3-BEED-E5DFF7EC13E4}"/>
+    <hyperlink ref="I147" r:id="rId15" xr:uid="{67CCFD3A-D3CB-4A94-B0E5-3634235BC3EA}"/>
+    <hyperlink ref="I148" r:id="rId16" xr:uid="{8E62DC48-8448-426E-BF8D-9DA1101F02D8}"/>
+    <hyperlink ref="I149" r:id="rId17" xr:uid="{99981094-7FC6-4754-9372-6CA07364CF17}"/>
+    <hyperlink ref="I150:I152" r:id="rId18" display="https://production-tailoy-repo-magento-statics.s3.amazonaws.com/imagenes/872x872/productos/i/a/n/antivirus-kaspersky-premium-10-dispositivos-2-anos-69606-default-1.jpg" xr:uid="{36C26BAA-89AC-4AF3-B0BE-D1F46C3523D3}"/>
+    <hyperlink ref="I66" r:id="rId19" xr:uid="{7E45C6FB-35DE-4723-800B-AC36B407BEBE}"/>
+    <hyperlink ref="I154" r:id="rId20" xr:uid="{234DB036-E655-484A-A5EB-6C9CAA3397EF}"/>
+    <hyperlink ref="I116" r:id="rId21" xr:uid="{B6A80480-5CD4-4C3E-80BF-0AC484902FC9}"/>
+    <hyperlink ref="I146" r:id="rId22" xr:uid="{FDE00E9F-E9D7-4F6D-84CF-E74FF647C404}"/>
+    <hyperlink ref="I108" r:id="rId23" xr:uid="{FE47A1B0-EBAA-42E2-A121-ABE74DE0175F}"/>
+    <hyperlink ref="I153" r:id="rId24" xr:uid="{7DAF1DB8-167E-4413-8B5E-16E91C8238CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>

--- a/digicode.xlsx
+++ b/digicode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\On Line - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD402A5-D807-4042-80A0-37570229B314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF88E9A-9393-4D92-8B3E-407591FC6C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2894,7 +2894,7 @@
     </filterColumn>
     <filterColumn colId="4">
       <filters>
-        <filter val="INTELIGENCIA ARTIFICIAL"/>
+        <filter val="CHATGPT"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3704,7 +3704,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>631</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>609</v>
+        <v>10</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>626</v>
@@ -3828,7 +3828,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>633</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>609</v>
+        <v>10</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>626</v>
@@ -4355,7 +4355,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>647</v>
       </c>
@@ -4386,7 +4386,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>643</v>
       </c>
@@ -4417,7 +4417,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>644</v>
       </c>
@@ -4448,7 +4448,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>646</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>642</v>
       </c>
@@ -4510,7 +4510,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>642</v>
       </c>
@@ -4541,7 +4541,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>645</v>
       </c>
@@ -7651,7 +7651,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K95 K101 K129 K140:K142 K2:K92">
+  <conditionalFormatting sqref="K2:K92 K95 K101 K129 K140:K142">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"OFICIAL"</formula>
     </cfRule>
